--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488014_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488014_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>C. RAMON PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5646</v>
+        <v>3.4373</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9055</v>
+        <v>4.5086</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3409</v>
+        <v>-1.0713</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6746</v>
+        <v>3.859</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4198</v>
+        <v>1.3203</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2548</v>
+        <v>2.5387</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2657</v>
+        <v>3.8576</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2208</v>
+        <v>1.3588</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4866</v>
+        <v>2.4988</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4089</v>
+        <v>0.0014</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6407</v>
+        <v>-0.0385</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2317</v>
+        <v>0.0399</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9911</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3062</v>
+        <v>-1.173</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4347</v>
+        <v>0.1506</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1285</v>
+        <v>-1.3236</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4074</v>
+        <v>1.5441</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4033</v>
+        <v>2.6808</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.8107</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. RAMON PEREZ</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8613</v>
+        <v>3.3825</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1011</v>
+        <v>4.2569</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2398</v>
+        <v>-0.8744</v>
       </c>
       <c r="G3" t="n">
-        <v>3.859</v>
+        <v>1.6746</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3203</v>
+        <v>0.4198</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5387</v>
+        <v>1.2548</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8576</v>
+        <v>1.2657</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3588</v>
+        <v>-0.2208</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4988</v>
+        <v>1.4866</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0014</v>
+        <v>0.4089</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0385</v>
+        <v>0.6407</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0399</v>
+        <v>-0.2317</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7489</v>
+        <v>1.1241</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2568</v>
+        <v>1.7861</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4921</v>
+        <v>-0.662</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5441</v>
+        <v>-0.4074</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6808</v>
+        <v>1.4033</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1367</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8594</v>
+        <v>1.7928</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2793</v>
+        <v>1.3811</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.4117</v>
       </c>
       <c r="G4" t="n">
         <v>0.5282</v>
@@ -766,13 +766,13 @@
         <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.083</v>
+        <v>-0.1496</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1042</v>
+        <v>-0.0643</v>
       </c>
       <c r="V4" t="n">
         <v>1.8107</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7000999999999999</v>
+        <v>1.7241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8887</v>
+        <v>1.7709</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1886</v>
+        <v>-0.0469</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3381</v>
+        <v>0.8111</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8868</v>
+        <v>0.0723</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4513</v>
+        <v>0.7388</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9142</v>
+        <v>0.8756</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3121</v>
+        <v>0.0409</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3979</v>
+        <v>0.8347</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4239</v>
+        <v>-0.0645</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5747</v>
+        <v>0.0314</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8492</v>
+        <v>-0.0959</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9911</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1982</v>
+        <v>-4.1627</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.8737</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1727</v>
+        <v>0.2296</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7246</v>
+        <v>-1.1033</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0772</v>
+        <v>4.5619</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.8284</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0772</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. YELAMOS MAÑAS</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6027</v>
+        <v>0.9214</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6027</v>
+        <v>1.1943</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.2729</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6027</v>
+        <v>2.3381</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.8868</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6027</v>
+        <v>0.4513</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6027</v>
+        <v>0.9142</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3121</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6027</v>
+        <v>-0.3979</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.4239</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.5747</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.8492</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.3305</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4783</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.8088</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>J. YELAMOS MAÑAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4951</v>
+        <v>0.6027</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1597</v>
+        <v>0.6027</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6646</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8111</v>
+        <v>0.6027</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0723</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7388</v>
+        <v>0.6027</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8756</v>
+        <v>0.6027</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0409</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8347</v>
+        <v>0.6027</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0645</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0314</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0959</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7751</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1027</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3816</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7211</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>4.5619</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.8284</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0536</v>
+        <v>-0.3207</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3562</v>
+        <v>-0.7637</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3026</v>
+        <v>0.443</v>
       </c>
       <c r="G8" t="n">
         <v>0.9012</v>
@@ -1078,13 +1078,13 @@
         <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1046</v>
+        <v>-0.1625</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5543</v>
+        <v>0.1469</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4497</v>
+        <v>-0.3093</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9704</v>
+        <v>-0.7385</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.249</v>
+        <v>-0.2209</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3834</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.587</v>
+        <v>-0.3552</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0624</v>
+        <v>0.1413</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5246</v>
+        <v>-0.4965</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2429</v>
+        <v>-3.1972</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8373</v>
+        <v>-1.7354</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4056</v>
+        <v>-1.4618</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6511</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5918</v>
+        <v>-0.5461</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4046</v>
+        <v>-0.4607</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2071</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5478</v>
+        <v>-3.2421</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5769</v>
+        <v>-0.2713</v>
       </c>
       <c r="F11" t="n">
         <v>-2.9708</v>
@@ -1312,10 +1312,10 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5543</v>
+        <v>-0.2487</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1872</v>
+        <v>0.1184</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3671</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7063</v>
+        <v>-3.355</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5944</v>
+        <v>-4.1869</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8881</v>
+        <v>0.8319</v>
       </c>
       <c r="G12" t="n">
         <v>-1.437</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3664</v>
+        <v>-1.0151</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.132</v>
+        <v>0.2754</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2344</v>
+        <v>-1.2905</v>
       </c>
       <c r="V12" t="n">
         <v>1.2775</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2961</v>
+        <v>-3.741</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5662</v>
+        <v>-2.955</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7298</v>
+        <v>-0.786</v>
       </c>
       <c r="G13" t="n">
         <v>2.9151</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9186</v>
+        <v>-0.3635</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8112</v>
+        <v>-0.1999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1074</v>
+        <v>-0.1636</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.733900000000001</v>
+        <v>-2.733700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.284699999999998</v>
+        <v>3.284600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.018300000000001</v>
+        <v>-6.0184</v>
       </c>
       <c r="G14" t="n">
         <v>10.9142</v>
@@ -1519,7 +1519,7 @@
         <v>5.4617</v>
       </c>
       <c r="J14" t="n">
-        <v>5.755599999999999</v>
+        <v>5.755600000000001</v>
       </c>
       <c r="K14" t="n">
         <v>3.2388</v>
@@ -1552,7 +1552,7 @@
         <v>2.9561</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.049900000000001</v>
+        <v>-7.0497</v>
       </c>
       <c r="V14" t="n">
         <v>1.348</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0098</v>
+        <v>4.1006</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1265</v>
+        <v>1.8118</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1167</v>
+        <v>2.2887</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4403</v>
+        <v>0.7761</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9608</v>
+        <v>-0.3051</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5205</v>
+        <v>1.0812</v>
       </c>
       <c r="J15" t="n">
-        <v>2.601</v>
+        <v>0.6616</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4766</v>
+        <v>0.2767</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1244</v>
+        <v>0.3849</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1608</v>
+        <v>0.1145</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5158</v>
+        <v>-0.5818</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6449</v>
+        <v>0.6962</v>
       </c>
       <c r="P15" t="n">
-        <v>1.784</v>
+        <v>2.5769</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9733</v>
+        <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5207</v>
+        <v>0.8683</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6485</v>
+        <v>1.3484</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8722</v>
+        <v>-0.4801</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7352</v>
+        <v>-0.1207</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0663</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.8015</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0057</v>
+        <v>3.853</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5243</v>
+        <v>2.2973</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5186</v>
+        <v>1.5557</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8979</v>
+        <v>-0.0664</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4941</v>
+        <v>-0.5773</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4039</v>
+        <v>0.5109</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7333</v>
+        <v>0.6926</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9743000000000001</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2411</v>
+        <v>0.6182</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1647</v>
+        <v>-0.759</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5198</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6449</v>
+        <v>-0.1073</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5858</v>
+        <v>2.9733</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7751</v>
+        <v>3.1716</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1542</v>
+        <v>-0.1403</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0853</v>
+        <v>0.5959</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9311</v>
+        <v>-0.7362</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1636</v>
+        <v>1.0864</v>
       </c>
       <c r="W16" t="n">
-        <v>5.3616</v>
+        <v>1.2071</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1979</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4913</v>
+        <v>3.2012</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9917</v>
+        <v>4.6075</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4995</v>
+        <v>-1.4062</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0664</v>
+        <v>-1.8979</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5773</v>
+        <v>-1.4941</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5109</v>
+        <v>-0.4039</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6926</v>
+        <v>-0.7333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07439999999999999</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6182</v>
+        <v>0.2411</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.759</v>
+        <v>-1.1647</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.5198</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1073</v>
+        <v>-0.6449</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9733</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1716</v>
+        <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5021</v>
+        <v>0.3497</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2903</v>
+        <v>1.1685</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7923</v>
+        <v>-0.8187</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0864</v>
+        <v>3.1636</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2071</v>
+        <v>5.3616</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1207</v>
+        <v>-2.1979</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5588</v>
+        <v>2.3701</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6913</v>
+        <v>3.4134</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8676</v>
+        <v>-1.0433</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7761</v>
+        <v>1.4403</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3051</v>
+        <v>1.9608</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0812</v>
+        <v>-0.5205</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6616</v>
+        <v>2.601</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2767</v>
+        <v>2.4766</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3849</v>
+        <v>0.1244</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1145</v>
+        <v>-1.1608</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5818</v>
+        <v>-0.5158</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6962</v>
+        <v>-0.6449</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5769</v>
+        <v>1.784</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7751</v>
+        <v>2.9733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6734</v>
+        <v>0.8811</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2279</v>
+        <v>0.9354</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9013</v>
+        <v>-0.0544</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1207</v>
+        <v>-1.7352</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0663</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1207</v>
+        <v>-2.8015</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2451</v>
+        <v>-0.6068</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9555</v>
+        <v>0.6499</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2005</v>
+        <v>-1.2567</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4241</v>
@@ -2014,13 +2014,13 @@
         <v>0.3964</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0492</v>
+        <v>0.6874</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0463</v>
+        <v>0.7407</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0029</v>
+        <v>-0.0533</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2666</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0957</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1556</v>
+        <v>0.2027</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0599</v>
+        <v>-0.8524</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6812</v>
+        <v>-0.4307</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7668</v>
+        <v>0.5945</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9145</v>
+        <v>-1.0252</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1572</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6388</v>
+        <v>0.4508</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5184</v>
+        <v>-0.3745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5241</v>
+        <v>-0.5069</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.128</v>
+        <v>0.1437</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3961</v>
+        <v>-0.6506</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1479</v>
+        <v>-0.2101</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0072</v>
+        <v>-0.0191</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1406</v>
+        <v>-0.191</v>
       </c>
       <c r="V21" t="n">
-        <v>0.337</v>
+        <v>-0.6036</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X21" t="n">
-        <v>0.337</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5665</v>
+        <v>-0.7973</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7141</v>
+        <v>-2.0537</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8524</v>
+        <v>1.2564</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4307</v>
+        <v>-1.6812</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5945</v>
+        <v>-0.7668</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0252</v>
+        <v>-0.9145</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07630000000000001</v>
+        <v>-1.1572</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4508</v>
+        <v>-0.6388</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3745</v>
+        <v>-0.5184</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5069</v>
+        <v>-0.5241</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1437</v>
+        <v>-0.128</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6506</v>
+        <v>-0.3961</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1269</v>
+        <v>0.1506</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0.0946</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.191</v>
+        <v>0.0559</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6036</v>
+        <v>0.337</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7403</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0115</v>
+        <v>-1.2536</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9328</v>
+        <v>-1.0042</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0787</v>
+        <v>-0.2494</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7712</v>
+        <v>-1.7652</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-1.7175</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0006</v>
+        <v>-0.0477</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2375</v>
+        <v>-1.5071</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6388</v>
+        <v>-1.3179</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5988</v>
+        <v>-0.1892</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5337</v>
+        <v>-0.2581</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1319</v>
+        <v>-0.3996</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4018</v>
+        <v>0.1415</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5793</v>
+        <v>0.2359</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3047</v>
+        <v>0.503</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2745</v>
+        <v>-0.2671</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8107</v>
+        <v>-0.1207</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8107</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>N. ALVAREZ ALVAREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1528</v>
+        <v>-1.865</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8191</v>
+        <v>-0.8005</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3337</v>
+        <v>-1.0646</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7652</v>
+        <v>-0.8149</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7175</v>
+        <v>0.0901</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0477</v>
+        <v>-0.9049</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5071</v>
+        <v>-0.6188</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3179</v>
+        <v>0.0202</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1892</v>
+        <v>-0.639</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2581</v>
+        <v>-0.1961</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3996</v>
+        <v>0.0699</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1415</v>
+        <v>-0.266</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6633</v>
+        <v>0.1569</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.312</v>
+        <v>0.0165</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3513</v>
+        <v>0.1404</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1207</v>
+        <v>-1.2071</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1207</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. ALVAREZ ALVAREZ</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.153</v>
+        <v>-2.2714</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0042</v>
+        <v>-1.1365</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1488</v>
+        <v>-1.1348</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8149</v>
+        <v>-1.7712</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0901</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9049</v>
+        <v>-1.0006</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6188</v>
+        <v>-1.2375</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0202</v>
+        <v>-0.6388</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.639</v>
+        <v>-0.5988</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1961</v>
+        <v>-0.5337</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0699</v>
+        <v>-0.1319</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.266</v>
+        <v>-0.4018</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.131</v>
+        <v>0.3194</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1872</v>
+        <v>0.101</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0562</v>
+        <v>0.2184</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.7099</v>
+        <v>-3.95</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5848</v>
+        <v>-2.9091</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1251</v>
+        <v>-1.0409</v>
       </c>
       <c r="G26" t="n">
         <v>-3.8816</v>
@@ -2482,13 +2482,13 @@
         <v>2.1805</v>
       </c>
       <c r="S26" t="n">
-        <v>2.0349</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8892</v>
+        <v>1.5649</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.7701</v>
       </c>
       <c r="V26" t="n">
         <v>-0.0704</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2.7338</v>
+        <v>2.733799999999998</v>
       </c>
       <c r="E27" t="n">
-        <v>5.681399999999998</v>
+        <v>5.6813</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.9475</v>
+        <v>-2.947499999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-10.9141</v>
@@ -2530,7 +2530,7 @@
         <v>-5.4527</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.4616</v>
+        <v>-5.461599999999999</v>
       </c>
       <c r="J27" t="n">
         <v>-5.1585</v>
@@ -2560,13 +2560,13 @@
         <v>18.8311</v>
       </c>
       <c r="S27" t="n">
-        <v>4.0937</v>
+        <v>4.0938</v>
       </c>
       <c r="T27" t="n">
-        <v>7.049800000000001</v>
+        <v>7.0498</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.9561</v>
+        <v>-2.9562</v>
       </c>
       <c r="V27" t="n">
         <v>-1.348</v>
